--- a/message_ix/tests/data/westeros_macro_input.xlsx
+++ b/message_ix/tests/data/westeros_macro_input.xlsx
@@ -1,29 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zakeri\Documents\Github\message_ix\message_ix\tests\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE44DA44-539A-4418-80D6-1165D2CDF36A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="979" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="12270" tabRatio="979" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="price_ref" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="cost_ref" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="demand_ref" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="lotol" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="esub" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="drate" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="depr" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="kpvs" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="kgdp" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="gdp_calibrate" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="aeei" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="MERtoPPP" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="config" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="price_ref" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_ref" sheetId="2" r:id="rId2"/>
+    <sheet name="demand_ref" sheetId="3" r:id="rId3"/>
+    <sheet name="lotol" sheetId="4" r:id="rId4"/>
+    <sheet name="esub" sheetId="5" r:id="rId5"/>
+    <sheet name="drate" sheetId="6" r:id="rId6"/>
+    <sheet name="depr" sheetId="7" r:id="rId7"/>
+    <sheet name="kpvs" sheetId="8" r:id="rId8"/>
+    <sheet name="kgdp" sheetId="9" r:id="rId9"/>
+    <sheet name="gdp_calibrate" sheetId="10" r:id="rId10"/>
+    <sheet name="aeei" sheetId="11" r:id="rId11"/>
+    <sheet name="MERtoPPP" sheetId="12" r:id="rId12"/>
+    <sheet name="config" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -32,89 +43,82 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="17">
-  <si>
-    <t xml:space="preserve">node</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sector</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Westeros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 more than value in first period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reduced from value found in COST_NODAL_NET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 less than first period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">taken from existing macro data files</t>
-  </si>
-  <si>
-    <t xml:space="preserve">year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not sure what to put as variable GDP DNE for Westeros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">just made up, but taken from existing macro data files</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ignore_nodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ignore_sectors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bar</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="21">
+  <si>
+    <t>node</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>Westeros</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>15 more than value in first period</t>
+  </si>
+  <si>
+    <t>reduced from value found in COST_NODAL_NET</t>
+  </si>
+  <si>
+    <t>10 less than first period</t>
+  </si>
+  <si>
+    <t>taken from existing macro data files</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>not sure what to put as variable GDP DNE for Westeros</t>
+  </si>
+  <si>
+    <t>just made up, but taken from existing macro data files</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>useful</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>USD/kWa</t>
+  </si>
+  <si>
+    <t>G$</t>
+  </si>
+  <si>
+    <t>GWa</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>T$</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00E+00"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,7 +130,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -134,68 +138,337 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="3" width="8.42578125"/>
+    <col min="5" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -206,46 +479,45 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>195</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="3" width="8.42578125"/>
+    <col min="5" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -256,102 +528,113 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>680</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>350</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="1">
         <v>690</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="1">
         <v>500</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="1">
         <v>700</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="1">
         <v>1000</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="1">
         <v>710</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="1">
         <v>2000</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="1">
         <v>720</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="1">
         <v>3000</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="4" width="8.42578125"/>
+    <col min="6" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -365,100 +648,108 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>690</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4">
         <v>0.02</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="1">
         <v>700</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4">
         <v>0.02</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="1">
         <v>710</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4">
         <v>0.02</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="1">
         <v>720</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="4">
         <v>0.02</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="3" width="8.42578125"/>
+    <col min="5" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,94 +760,103 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>700</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="1">
         <v>710</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="1">
         <v>1.8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="1">
         <v>720</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="12.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="11.3418367346939"/>
+    <col min="1" max="1025" width="11.28515625"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="0" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -564,17 +864,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="2" width="8.42578125"/>
+    <col min="4" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,44 +880,43 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <f aca="false">15/1000</f>
-        <v>0.015</v>
+      <c r="B2" s="1">
+        <f>15/1000</f>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="3" width="8.42578125"/>
+    <col min="5" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,46 +927,45 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="2" width="8.42578125"/>
+    <col min="4" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -677,43 +973,42 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>0.05</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="2" width="8.42578125"/>
+    <col min="4" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,43 +1016,42 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>0.2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="2" width="8.42578125"/>
+    <col min="4" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -765,43 +1059,42 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>0.05</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="2" width="8.42578125"/>
+    <col min="4" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,43 +1102,42 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>0.05</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="2" width="8.42578125"/>
+    <col min="4" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,43 +1145,42 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>0.3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1025" min="1" style="0" width="8.36734693877551"/>
+    <col min="1" max="2" width="8.42578125"/>
+    <col min="4" max="1026" width="8.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -897,27 +1188,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>